--- a/backend/data/financials_by_company/0254.HK.xlsx
+++ b/backend/data/financials_by_company/0254.HK.xlsx
@@ -3049,187 +3049,187 @@
       </c>
       <c r="CT1" t="inlineStr">
         <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="CV1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="CW1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
         </is>
       </c>
       <c r="EE1" t="inlineStr">
@@ -3322,64 +3322,64 @@
         <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1</v>
+        <v>0.116</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1</v>
+        <v>0.116</v>
       </c>
       <c r="U2" t="n">
-        <v>1.07</v>
+        <v>0.106</v>
       </c>
       <c r="V2" t="n">
-        <v>1.14</v>
+        <v>0.116</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1</v>
+        <v>0.116</v>
       </c>
       <c r="X2" t="n">
-        <v>1.1</v>
+        <v>0.116</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.07</v>
+        <v>0.106</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.14</v>
+        <v>0.116</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.215</v>
+        <v>0.263</v>
       </c>
       <c r="AC2" t="n">
-        <v>98828358</v>
+        <v>18500000</v>
       </c>
       <c r="AD2" t="n">
-        <v>98828358</v>
+        <v>18500000</v>
       </c>
       <c r="AE2" t="n">
-        <v>6912150</v>
+        <v>19035190</v>
       </c>
       <c r="AF2" t="n">
-        <v>31903010</v>
+        <v>84465651</v>
       </c>
       <c r="AG2" t="n">
-        <v>31903010</v>
+        <v>84465651</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.1</v>
+        <v>0.107</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.09</v>
+        <v>0.108</v>
       </c>
       <c r="AJ2" t="n">
-        <v>750096704</v>
+        <v>71630856</v>
       </c>
       <c r="AK2" t="n">
-        <v>743339124</v>
+        <v>72306623</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.26</v>
+        <v>0.104</v>
       </c>
       <c r="AM2" t="n">
         <v>1.2</v>
@@ -3388,16 +3388,16 @@
         <v>472.8872</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.24</v>
+        <v>0.104</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.136934999999999</v>
+        <v>0.8725362</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.7904</v>
+        <v>0.76618</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.572975</v>
+        <v>0.5813199999999999</v>
       </c>
       <c r="AS2" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>704801728</v>
+        <v>138783856</v>
       </c>
       <c r="AX2" t="n">
         <v>-0.78393</v>
@@ -3438,7 +3438,7 @@
         <v>0.211</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.2606635</v>
+        <v>0.5023697</v>
       </c>
       <c r="BF2" t="n">
         <v>1751241600</v>
@@ -3464,16 +3464,16 @@
         <v>1755216000</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.585000000000001</v>
+        <v>1.691</v>
       </c>
       <c r="BN2" t="n">
-        <v>-246.348</v>
+        <v>-48.509</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.6829269</v>
+        <v>-0.7100000400000001</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         </is>
       </c>
       <c r="BR2" t="n">
-        <v>1.11</v>
+        <v>0.106</v>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
@@ -3581,139 +3581,139 @@
         </is>
       </c>
       <c r="CT2" t="n">
-        <v>0.90909004</v>
+        <v>-0.66018</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.11</v>
+        <v>-0.8616513</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.00999999</v>
-      </c>
-      <c r="CW2" t="inlineStr">
-        <is>
-          <t>1.07 - 1.14</t>
-        </is>
-      </c>
-      <c r="CX2" t="inlineStr">
+        <v>-0.47531998</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>-0.81765634</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>15</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>15</v>
+      </c>
+      <c r="CZ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>1191547800000</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>-0.009999998</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>0.106 - 0.116</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="CY2" t="n">
-        <v>6912150</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>3.269231</v>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>0.26 - 1.2</t>
-        </is>
-      </c>
-      <c r="DC2" t="n">
-        <v>-0.09000002999999999</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>-0.075000025</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>168.2927</v>
-      </c>
       <c r="DF2" t="n">
-        <v>1740491316</v>
+        <v>19035190</v>
       </c>
       <c r="DG2" t="n">
-        <v>1740491316</v>
-      </c>
-      <c r="DH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>-0.14</v>
+        <v>0.0019999966</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>0.019230736</v>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>0.104 - 1.2</t>
+        </is>
       </c>
       <c r="DJ2" t="n">
-        <v>0.3196</v>
+        <v>-1.0940001</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.4043522</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0.53702503</v>
+        <v>-0.9116667000000001</v>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="DM2" t="n">
-        <v>0.9372574</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>15</v>
+        <v>1783066093</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>finmb_4481694</t>
+        </is>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
-          <t>NUR HOLDINGS</t>
+          <t>Asia/Hong_Kong</t>
         </is>
       </c>
       <c r="DQ2" t="inlineStr">
         <is>
-          <t>National United Resources Holdings Limited</t>
-        </is>
-      </c>
-      <c r="DR2" t="b">
-        <v>0</v>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DR2" t="n">
+        <v>28800000</v>
       </c>
       <c r="DS2" t="inlineStr">
         <is>
-          <t>PREPRE</t>
+          <t>hk_market</t>
         </is>
       </c>
       <c r="DT2" t="b">
         <v>0</v>
       </c>
-      <c r="DU2" t="n">
-        <v>1191547800000</v>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
       </c>
       <c r="DV2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DW2" t="n">
-        <v>1782115692</v>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>finmb_4481694</t>
-        </is>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
+          <t>NUR HOLDINGS</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>National United Resources Holdings Limited</t>
+        </is>
+      </c>
+      <c r="DX2" t="n">
+        <v>-71</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>1740491316</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>1740491316</v>
+      </c>
+      <c r="EA2" t="b">
+        <v>0</v>
       </c>
       <c r="EB2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="ED2" t="b">
-        <v>0</v>
+        <v>-0.14</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>-8.620687999999999</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>0.106</v>
       </c>
       <c r="EE2" t="inlineStr"/>
     </row>
